--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00155_18880712.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="oocihm.N_00155_18880712.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\preprocess-notiles-paddleocr-paddlevl\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
+          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00155_18880712\oocihm.N_00155_18880712.8.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -983,7 +983,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.8.xlsx
+++ b/4-multi-document-abbyy-vs-notiles-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00155_18880712/oocihm.N_00155_18880712.8.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="oocihm.N_00155_18880712.8" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="oocihm.N_00155_18880712.8" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y89"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
-    <col width="50" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="60" customWidth="1" min="18" max="18"/>
@@ -613,24 +613,28 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L15: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: EMPEROR FREDERICKâ€™S LARYNX.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
-          <t>L93: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L93: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>611</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,12 +704,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L26: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of gentlemen, seated in front of the Queenâ€™s</t>
+          <t>L359: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: II Al IDD • fifteen teachers, male or</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -723,7 +727,7 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: -- - - - - - - - - - - would ask you as a special favor to call and examine our stock. By doing so you will save from so to 00 - cent., at WOODâ€™S FAIR,</t>
+          <t>L178: punctuation artifact: double/multiple hyphen :: -- - - - - - - - - - - would ask you as a special favor to call and examine our stock. By doing so you will save from so to 00 - cent., at WOOD’S FAIR,</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
@@ -756,14 +760,14 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>4351</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr"/>
       <c r="E4" s="1" t="inlineStr"/>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>L299: candidate OCR token mismatch vs other OCR: "PicH" vs "PINCH" :: WooD Â· PicH.- At the residence of the bride's</t>
+          <t>L299: candidate OCR token mismatch vs other OCR: "PicH" vs "PINCH" :: WooD · PicH.- At the residence of the bride's</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr"/>
@@ -779,19 +783,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” FOR</t>
+          <t>L518: stray/suspicious non-ASCII glyph(s): U+53F8 CJK UNIFIED IDEOGRAPH-53F8 | isolated marker/symbol line :: 司</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L104: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Frederickâ€™s throat after the piece had been</t>
+          <t>L379: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • IS!</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L152: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -808,7 +812,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L383: line starts with punctuation glued to text :: __FOR YOUR -</t>
+          <t>L379: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • IS!</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -830,12 +834,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>58</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>65</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -856,14 +860,10 @@
           <t>L154: suspicious token(s): 8c (letter/digit mix), 45c (letter/digit mix) :: OFF AT AN IMMENSE REDUCTION on former prices. Alarge Verio there will surprise you. Trimming at 8c., formerly sold for 45c. Beaded Trimmings less</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L277: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” USE</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 85o (letter/digit mix) :: finest Stove in the market. A good one at 85o. Ladiesâ€™ Collarsand Cuffs at popular lline of Fiteworka especially adapted for boating or to illuminate your summer</t>
+          <t>L388: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: @LARDINE MACHINE OIL.®</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -881,13 +881,13 @@
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: KINGSTON, July 9.â€”The shock of earth-.___________---------------------------------------------</t>
+          <t>L334: punctuation artifact: double/multiple hyphen :: KINGSTON, July 9.—The shock of earth-.___________---------------------------------------------</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L392: line starts with punctuation glued to text :: __your m^ use only Landing</t>
+          <t>L383: line starts with punctuation glued to text :: __FOR YOUR -</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
@@ -935,14 +935,10 @@
           <t>L156: suspicious token(s): 50c (letter/digit mix), 60c (letter/digit mix), 8c (letter/digit mix), 15c (letter/digit mix) :: 50c. and 60c. Daisy Wreaths only 8c., formerly 15c. Untrimmed Ha GAINS DISPLAYED IN THE CARPET ROOMS, about one hundred remnants of Brussels,</t>
         </is>
       </c>
-      <c r="J6" s="1" t="inlineStr">
-        <is>
-          <t>L315: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: McKay-Buchan.â€” On the 4th July, at the resi-</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr"/>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L178: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: -- - - - - - - - - - - would ask you as a special favor to call and examine our stock. By doing so you will save from so to 00 - cent., at WOODâ€™S FAIR,</t>
+          <t>L564: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • located at</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -966,7 +962,7 @@
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L749: line starts with digit/letter garbage token | suspicious token(s): 1Lot (letter/digit mix) :: 1Lot Fifteen, Concession Seven, in township</t>
+          <t>L392: line starts with punctuation glued to text :: __your m^ use only Landing</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1010,16 +1006,8 @@
           <t>L167: line starts with digit/letter garbage token | suspicious token(s): 1the (letter/digit mix) :: 1the latest novels by the best authors, we will offer during this month the entire lot</t>
         </is>
       </c>
-      <c r="J7" s="1" t="inlineStr">
-        <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA | isolated marker/symbol line :: å�¸</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L179: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 66 and 68 King street west, Hamilton, Ont. ________________________________â€”</t>
-        </is>
-      </c>
+      <c r="J7" s="1" t="inlineStr"/>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1035,13 +1023,13 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” USE --------------</t>
+          <t>L386: punctuation artifact: double/multiple hyphen :: — USE --------------</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L762: line starts with punctuation glued to text :: ____Mr. John Buckwell, operator at the</t>
+          <t>L564: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • located at</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1082,11 +1070,7 @@
         </is>
       </c>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): ITarrant (odd internal casing) :: ITarrantâ€™s</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -1104,7 +1088,7 @@
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L774: line starts with digit/letter garbage token | suspicious token(s): 1man (letter/digit mix) :: 1man named Fitzpatrick, was tried before</t>
+          <t>L749: line starts with digit/letter garbage token | suspicious token(s): 1Lot (letter/digit mix) :: 1Lot Fifteen, Concession Seven, in township</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1145,11 +1129,7 @@
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L211: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: getting oor provisions, and in gaâ€™in alang 8 1</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1167,7 +1147,7 @@
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L775: line starts with digit/letter garbage token | suspicious token(s): 1Judge (letter/digit mix) :: 1Judge Sinclair Tuesday morning and</t>
+          <t>L762: line starts with punctuation glued to text :: ____Mr. John Buckwell, operator at the</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1185,12 +1165,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1208,11 +1188,7 @@
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: dow, says : Â« Guid keep us, Jeems ! dâ€™ye</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1228,7 +1204,11 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>L774: line starts with digit/letter garbage token | suspicious token(s): 1man (letter/digit mix) :: 1man named Fitzpatrick, was tried before</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr"/>
       <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
@@ -1249,7 +1229,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1267,16 +1247,12 @@
         </is>
       </c>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L217: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: my specs. "Thatâ€™s extraornar;</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L518: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER, U+00B8 CEDILLA | isolated marker/symbol line :: å�¸</t>
+          <t>L518: stray/suspicious non-ASCII glyph(s): U+53F8 CJK UNIFIED IDEOGRAPH-53F8 | isolated marker/symbol line :: 司</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1287,7 +1263,11 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>L775: line starts with digit/letter garbage token | suspicious token(s): 1Judge (letter/digit mix) :: 1Judge Sinclair Tuesday morning and</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr"/>
       <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" s="1" t="inlineStr"/>
@@ -1322,15 +1302,11 @@
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>L175: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 85o (letter/digit mix) :: finest Stove in the market. A good one at 85o. Ladiesâ€™ Collarsand Cuffs at popular lline of Fiteworka especially adapted for boating or to illuminate your summer</t>
+          <t>L175: suspicious token(s): 85o (letter/digit mix) :: finest Stove in the market. A good one at 85o. Ladies’ Collarsand Cuffs at popular lline of Fiteworka especially adapted for boating or to illuminate your summer</t>
         </is>
       </c>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L218: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: trade must be dull atweel when theyâ€™ve</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1385,11 +1361,7 @@
         </is>
       </c>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: hoo can they afford aâ€˜ that gas and a big</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1426,7 +1398,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1440,15 +1412,11 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L192: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): ITarrant (odd internal casing) :: ITarrantâ€™s</t>
+          <t>L192: suspicious token(s): ITarrant’s (odd internal casing) :: ITarrant’s</t>
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L227: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: I'll go in and get eight punâ€™, and, after I</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
@@ -1503,11 +1471,7 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L229: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: eight punâ€™ ; it'll no look sae greedy like.</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
@@ -1562,11 +1526,7 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Jist wait a wee." And in I goes. "Iâ€™ll</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
@@ -1621,11 +1581,7 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L231: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: takâ€™ eight punâ€™ o' that sugar!" I says.</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
@@ -1668,11 +1624,7 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L235: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Iâ€™m sure I'm vera much obleeged tae ye</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
@@ -1715,11 +1667,7 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L236: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tae be see kind tae meâ€”me a perfect</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1762,11 +1710,7 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L242: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: ye" and wiâ€˜ that I made tae come oot.</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1805,11 +1749,7 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L245: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: counter, " yeâ€™ve forgot tea ! there s two</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr"/>
@@ -1844,11 +1784,7 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L246: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: pun' o' tea goes along wiâ€˜ that</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr"/>
@@ -1883,11 +1819,7 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L248: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Â« Lod save us, tea !â€”tea, did ye say?</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr"/>
@@ -1922,11 +1854,7 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L249: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Betty," I cries, " it's no only sugar theyâ€™re</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr"/>
@@ -1961,11 +1889,7 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L250: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: mein awaâ€™, but tea. Great criftens, this</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr"/>
@@ -2000,11 +1924,7 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L251: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: bates all! Tea! Certainly I'll takâ€™ the</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr"/>
@@ -2039,11 +1959,7 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tea," anâ€™ I held up the lid o' the basket, an</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr"/>
@@ -2078,11 +1994,7 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 64 Is there naethinâ€™ elseâ€”coffee, or any-</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr"/>
@@ -2117,11 +2029,7 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the Times, in which he and other Nationalist HEWSON.â€”At 9 Stinson street, on Saturday,</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr"/>
@@ -2152,11 +2060,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: He would also ask the Government to ap- GHENT â€”At Burlington, Ont., on the 3rd inst.,</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr"/>
@@ -2187,11 +2091,7 @@
       </c>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: unfounded charges made against him by SCHNABEL-TURKEY.â€”On Monday evening, July</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr"/>
@@ -2222,11 +2122,7 @@
       </c>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L305: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: The Canadian Pacific and Grand Trunk CRAIB-WORK.â€”On Wednesday, July 4th, at the</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr"/>
@@ -2257,11 +2153,7 @@
       </c>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L307: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Railways meet at that point. On Saturday, residence of the brideâ€™s father, 21 Magill street,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
@@ -2292,11 +2184,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: there, was playing on the track, and by dance of tho brideâ€™s brother-in-law, W. B.</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
@@ -2327,11 +2215,7 @@
       </c>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L312: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: fastened in a â€œfrog.â€� Hercrimbrouuld daughter ofthe late Thomas W. Daville. second</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
@@ -2362,11 +2246,7 @@
       </c>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L317: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: frantic efforts to tear his child from the KNIGHT.â€”In Geneva, N. Y., at the residence of</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
@@ -2382,1649 +2262,6 @@
       <c r="X36" s="1" t="inlineStr"/>
       <c r="Y36" s="1" t="inlineStr"/>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr"/>
-      <c r="B37" s="1" t="inlineStr"/>
-      <c r="C37" s="1" t="inlineStr"/>
-      <c r="D37" s="1" t="inlineStr"/>
-      <c r="E37" s="1" t="inlineStr"/>
-      <c r="F37" s="1" t="inlineStr"/>
-      <c r="G37" s="1" t="inlineStr"/>
-      <c r="H37" s="1" t="inlineStr"/>
-      <c r="I37" s="1" t="inlineStr"/>
-      <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L322: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: relinquish the child or lose his own life, SEABLEâ€” On the 7th inst., Alice Searle,</t>
-        </is>
-      </c>
-      <c r="L37" s="1" t="inlineStr"/>
-      <c r="M37" s="1" t="inlineStr"/>
-      <c r="N37" s="1" t="inlineStr"/>
-      <c r="O37" s="1" t="inlineStr"/>
-      <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
-      <c r="R37" s="1" t="inlineStr"/>
-      <c r="S37" s="1" t="inlineStr"/>
-      <c r="T37" s="1" t="inlineStr"/>
-      <c r="U37" s="1" t="inlineStr"/>
-      <c r="V37" s="1" t="inlineStr"/>
-      <c r="W37" s="1" t="inlineStr"/>
-      <c r="X37" s="1" t="inlineStr"/>
-      <c r="Y37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="1" t="inlineStr"/>
-      <c r="C38" s="1" t="inlineStr"/>
-      <c r="D38" s="1" t="inlineStr"/>
-      <c r="E38" s="1" t="inlineStr"/>
-      <c r="F38" s="1" t="inlineStr"/>
-      <c r="G38" s="1" t="inlineStr"/>
-      <c r="H38" s="1" t="inlineStr"/>
-      <c r="I38" s="1" t="inlineStr"/>
-      <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: KINGSTON, July 9.â€”The shock of earth-.___________---------------------------------------------</t>
-        </is>
-      </c>
-      <c r="L38" s="1" t="inlineStr"/>
-      <c r="M38" s="1" t="inlineStr"/>
-      <c r="N38" s="1" t="inlineStr"/>
-      <c r="O38" s="1" t="inlineStr"/>
-      <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="inlineStr"/>
-      <c r="S38" s="1" t="inlineStr"/>
-      <c r="T38" s="1" t="inlineStr"/>
-      <c r="U38" s="1" t="inlineStr"/>
-      <c r="V38" s="1" t="inlineStr"/>
-      <c r="W38" s="1" t="inlineStr"/>
-      <c r="X38" s="1" t="inlineStr"/>
-      <c r="Y38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr"/>
-      <c r="B39" s="1" t="inlineStr"/>
-      <c r="C39" s="1" t="inlineStr"/>
-      <c r="D39" s="1" t="inlineStr"/>
-      <c r="E39" s="1" t="inlineStr"/>
-      <c r="F39" s="1" t="inlineStr"/>
-      <c r="G39" s="1" t="inlineStr"/>
-      <c r="H39" s="1" t="inlineStr"/>
-      <c r="I39" s="1" t="inlineStr"/>
-      <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L338: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: whole district of the Grand Trunk the I BELLEVILLE, Ont., July 9.â€”A slight shock</t>
-        </is>
-      </c>
-      <c r="L39" s="1" t="inlineStr"/>
-      <c r="M39" s="1" t="inlineStr"/>
-      <c r="N39" s="1" t="inlineStr"/>
-      <c r="O39" s="1" t="inlineStr"/>
-      <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr"/>
-      <c r="R39" s="1" t="inlineStr"/>
-      <c r="S39" s="1" t="inlineStr"/>
-      <c r="T39" s="1" t="inlineStr"/>
-      <c r="U39" s="1" t="inlineStr"/>
-      <c r="V39" s="1" t="inlineStr"/>
-      <c r="W39" s="1" t="inlineStr"/>
-      <c r="X39" s="1" t="inlineStr"/>
-      <c r="Y39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr"/>
-      <c r="B40" s="1" t="inlineStr"/>
-      <c r="C40" s="1" t="inlineStr"/>
-      <c r="D40" s="1" t="inlineStr"/>
-      <c r="E40" s="1" t="inlineStr"/>
-      <c r="F40" s="1" t="inlineStr"/>
-      <c r="G40" s="1" t="inlineStr"/>
-      <c r="H40" s="1" t="inlineStr"/>
-      <c r="I40" s="1" t="inlineStr"/>
-      <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L359: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: II Al IDD â€¢ fifteen teachers, male or</t>
-        </is>
-      </c>
-      <c r="L40" s="1" t="inlineStr"/>
-      <c r="M40" s="1" t="inlineStr"/>
-      <c r="N40" s="1" t="inlineStr"/>
-      <c r="O40" s="1" t="inlineStr"/>
-      <c r="P40" s="1" t="inlineStr"/>
-      <c r="Q40" s="1" t="inlineStr"/>
-      <c r="R40" s="1" t="inlineStr"/>
-      <c r="S40" s="1" t="inlineStr"/>
-      <c r="T40" s="1" t="inlineStr"/>
-      <c r="U40" s="1" t="inlineStr"/>
-      <c r="V40" s="1" t="inlineStr"/>
-      <c r="W40" s="1" t="inlineStr"/>
-      <c r="X40" s="1" t="inlineStr"/>
-      <c r="Y40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr"/>
-      <c r="B41" s="1" t="inlineStr"/>
-      <c r="C41" s="1" t="inlineStr"/>
-      <c r="D41" s="1" t="inlineStr"/>
-      <c r="E41" s="1" t="inlineStr"/>
-      <c r="F41" s="1" t="inlineStr"/>
-      <c r="G41" s="1" t="inlineStr"/>
-      <c r="H41" s="1" t="inlineStr"/>
-      <c r="I41" s="1" t="inlineStr"/>
-      <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L379: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ IS!</t>
-        </is>
-      </c>
-      <c r="L41" s="1" t="inlineStr"/>
-      <c r="M41" s="1" t="inlineStr"/>
-      <c r="N41" s="1" t="inlineStr"/>
-      <c r="O41" s="1" t="inlineStr"/>
-      <c r="P41" s="1" t="inlineStr"/>
-      <c r="Q41" s="1" t="inlineStr"/>
-      <c r="R41" s="1" t="inlineStr"/>
-      <c r="S41" s="1" t="inlineStr"/>
-      <c r="T41" s="1" t="inlineStr"/>
-      <c r="U41" s="1" t="inlineStr"/>
-      <c r="V41" s="1" t="inlineStr"/>
-      <c r="W41" s="1" t="inlineStr"/>
-      <c r="X41" s="1" t="inlineStr"/>
-      <c r="Y41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr"/>
-      <c r="B42" s="1" t="inlineStr"/>
-      <c r="C42" s="1" t="inlineStr"/>
-      <c r="D42" s="1" t="inlineStr"/>
-      <c r="E42" s="1" t="inlineStr"/>
-      <c r="F42" s="1" t="inlineStr"/>
-      <c r="G42" s="1" t="inlineStr"/>
-      <c r="H42" s="1" t="inlineStr"/>
-      <c r="I42" s="1" t="inlineStr"/>
-      <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L386: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” USE --------------</t>
-        </is>
-      </c>
-      <c r="L42" s="1" t="inlineStr"/>
-      <c r="M42" s="1" t="inlineStr"/>
-      <c r="N42" s="1" t="inlineStr"/>
-      <c r="O42" s="1" t="inlineStr"/>
-      <c r="P42" s="1" t="inlineStr"/>
-      <c r="Q42" s="1" t="inlineStr"/>
-      <c r="R42" s="1" t="inlineStr"/>
-      <c r="S42" s="1" t="inlineStr"/>
-      <c r="T42" s="1" t="inlineStr"/>
-      <c r="U42" s="1" t="inlineStr"/>
-      <c r="V42" s="1" t="inlineStr"/>
-      <c r="W42" s="1" t="inlineStr"/>
-      <c r="X42" s="1" t="inlineStr"/>
-      <c r="Y42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr"/>
-      <c r="B43" s="1" t="inlineStr"/>
-      <c r="C43" s="1" t="inlineStr"/>
-      <c r="D43" s="1" t="inlineStr"/>
-      <c r="E43" s="1" t="inlineStr"/>
-      <c r="F43" s="1" t="inlineStr"/>
-      <c r="G43" s="1" t="inlineStr"/>
-      <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr"/>
-      <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L388: stray/suspicious non-ASCII glyph(s): U+00AE REGISTERED SIGN :: @LARDINE MACHINE OIL.Â®</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr"/>
-      <c r="M43" s="1" t="inlineStr"/>
-      <c r="N43" s="1" t="inlineStr"/>
-      <c r="O43" s="1" t="inlineStr"/>
-      <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
-      <c r="R43" s="1" t="inlineStr"/>
-      <c r="S43" s="1" t="inlineStr"/>
-      <c r="T43" s="1" t="inlineStr"/>
-      <c r="U43" s="1" t="inlineStr"/>
-      <c r="V43" s="1" t="inlineStr"/>
-      <c r="W43" s="1" t="inlineStr"/>
-      <c r="X43" s="1" t="inlineStr"/>
-      <c r="Y43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr"/>
-      <c r="B44" s="1" t="inlineStr"/>
-      <c r="C44" s="1" t="inlineStr"/>
-      <c r="D44" s="1" t="inlineStr"/>
-      <c r="E44" s="1" t="inlineStr"/>
-      <c r="F44" s="1" t="inlineStr"/>
-      <c r="G44" s="1" t="inlineStr"/>
-      <c r="H44" s="1" t="inlineStr"/>
-      <c r="I44" s="1" t="inlineStr"/>
-      <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L397: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Wood &amp; Leggatâ€™s Hardware</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr"/>
-      <c r="M44" s="1" t="inlineStr"/>
-      <c r="N44" s="1" t="inlineStr"/>
-      <c r="O44" s="1" t="inlineStr"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="inlineStr"/>
-      <c r="R44" s="1" t="inlineStr"/>
-      <c r="S44" s="1" t="inlineStr"/>
-      <c r="T44" s="1" t="inlineStr"/>
-      <c r="U44" s="1" t="inlineStr"/>
-      <c r="V44" s="1" t="inlineStr"/>
-      <c r="W44" s="1" t="inlineStr"/>
-      <c r="X44" s="1" t="inlineStr"/>
-      <c r="Y44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr"/>
-      <c r="B45" s="1" t="inlineStr"/>
-      <c r="C45" s="1" t="inlineStr"/>
-      <c r="D45" s="1" t="inlineStr"/>
-      <c r="E45" s="1" t="inlineStr"/>
-      <c r="F45" s="1" t="inlineStr"/>
-      <c r="G45" s="1" t="inlineStr"/>
-      <c r="H45" s="1" t="inlineStr"/>
-      <c r="I45" s="1" t="inlineStr"/>
-      <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L403: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Stanley Mills &amp; Co.â€™s Hardware</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr"/>
-      <c r="M45" s="1" t="inlineStr"/>
-      <c r="N45" s="1" t="inlineStr"/>
-      <c r="O45" s="1" t="inlineStr"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="inlineStr"/>
-      <c r="R45" s="1" t="inlineStr"/>
-      <c r="S45" s="1" t="inlineStr"/>
-      <c r="T45" s="1" t="inlineStr"/>
-      <c r="U45" s="1" t="inlineStr"/>
-      <c r="V45" s="1" t="inlineStr"/>
-      <c r="W45" s="1" t="inlineStr"/>
-      <c r="X45" s="1" t="inlineStr"/>
-      <c r="Y45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr"/>
-      <c r="B46" s="1" t="inlineStr"/>
-      <c r="C46" s="1" t="inlineStr"/>
-      <c r="D46" s="1" t="inlineStr"/>
-      <c r="E46" s="1" t="inlineStr"/>
-      <c r="F46" s="1" t="inlineStr"/>
-      <c r="G46" s="1" t="inlineStr"/>
-      <c r="H46" s="1" t="inlineStr"/>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L436: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: J. A. Barr &amp; Co.â€™s Drug Store.</t>
-        </is>
-      </c>
-      <c r="L46" s="1" t="inlineStr"/>
-      <c r="M46" s="1" t="inlineStr"/>
-      <c r="N46" s="1" t="inlineStr"/>
-      <c r="O46" s="1" t="inlineStr"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="inlineStr"/>
-      <c r="S46" s="1" t="inlineStr"/>
-      <c r="T46" s="1" t="inlineStr"/>
-      <c r="U46" s="1" t="inlineStr"/>
-      <c r="V46" s="1" t="inlineStr"/>
-      <c r="W46" s="1" t="inlineStr"/>
-      <c r="X46" s="1" t="inlineStr"/>
-      <c r="Y46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr"/>
-      <c r="B47" s="1" t="inlineStr"/>
-      <c r="C47" s="1" t="inlineStr"/>
-      <c r="D47" s="1" t="inlineStr"/>
-      <c r="E47" s="1" t="inlineStr"/>
-      <c r="F47" s="1" t="inlineStr"/>
-      <c r="G47" s="1" t="inlineStr"/>
-      <c r="H47" s="1" t="inlineStr"/>
-      <c r="I47" s="1" t="inlineStr"/>
-      <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: McGregor &amp; Parkesâ€™ Drug Store.</t>
-        </is>
-      </c>
-      <c r="L47" s="1" t="inlineStr"/>
-      <c r="M47" s="1" t="inlineStr"/>
-      <c r="N47" s="1" t="inlineStr"/>
-      <c r="O47" s="1" t="inlineStr"/>
-      <c r="P47" s="1" t="inlineStr"/>
-      <c r="Q47" s="1" t="inlineStr"/>
-      <c r="R47" s="1" t="inlineStr"/>
-      <c r="S47" s="1" t="inlineStr"/>
-      <c r="T47" s="1" t="inlineStr"/>
-      <c r="U47" s="1" t="inlineStr"/>
-      <c r="V47" s="1" t="inlineStr"/>
-      <c r="W47" s="1" t="inlineStr"/>
-      <c r="X47" s="1" t="inlineStr"/>
-      <c r="Y47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr"/>
-      <c r="B48" s="1" t="inlineStr"/>
-      <c r="C48" s="1" t="inlineStr"/>
-      <c r="D48" s="1" t="inlineStr"/>
-      <c r="E48" s="1" t="inlineStr"/>
-      <c r="F48" s="1" t="inlineStr"/>
-      <c r="G48" s="1" t="inlineStr"/>
-      <c r="H48" s="1" t="inlineStr"/>
-      <c r="I48" s="1" t="inlineStr"/>
-      <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L440: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A. Vincent &amp; Co.â€™s Drug Store.</t>
-        </is>
-      </c>
-      <c r="L48" s="1" t="inlineStr"/>
-      <c r="M48" s="1" t="inlineStr"/>
-      <c r="N48" s="1" t="inlineStr"/>
-      <c r="O48" s="1" t="inlineStr"/>
-      <c r="P48" s="1" t="inlineStr"/>
-      <c r="Q48" s="1" t="inlineStr"/>
-      <c r="R48" s="1" t="inlineStr"/>
-      <c r="S48" s="1" t="inlineStr"/>
-      <c r="T48" s="1" t="inlineStr"/>
-      <c r="U48" s="1" t="inlineStr"/>
-      <c r="V48" s="1" t="inlineStr"/>
-      <c r="W48" s="1" t="inlineStr"/>
-      <c r="X48" s="1" t="inlineStr"/>
-      <c r="Y48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr"/>
-      <c r="B49" s="1" t="inlineStr"/>
-      <c r="C49" s="1" t="inlineStr"/>
-      <c r="D49" s="1" t="inlineStr"/>
-      <c r="E49" s="1" t="inlineStr"/>
-      <c r="F49" s="1" t="inlineStr"/>
-      <c r="G49" s="1" t="inlineStr"/>
-      <c r="H49" s="1" t="inlineStr"/>
-      <c r="I49" s="1" t="inlineStr"/>
-      <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: J. A. Clarkâ€™s Drug Store.</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr"/>
-      <c r="M49" s="1" t="inlineStr"/>
-      <c r="N49" s="1" t="inlineStr"/>
-      <c r="O49" s="1" t="inlineStr"/>
-      <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
-      <c r="R49" s="1" t="inlineStr"/>
-      <c r="S49" s="1" t="inlineStr"/>
-      <c r="T49" s="1" t="inlineStr"/>
-      <c r="U49" s="1" t="inlineStr"/>
-      <c r="V49" s="1" t="inlineStr"/>
-      <c r="W49" s="1" t="inlineStr"/>
-      <c r="X49" s="1" t="inlineStr"/>
-      <c r="Y49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr"/>
-      <c r="B50" s="1" t="inlineStr"/>
-      <c r="C50" s="1" t="inlineStr"/>
-      <c r="D50" s="1" t="inlineStr"/>
-      <c r="E50" s="1" t="inlineStr"/>
-      <c r="F50" s="1" t="inlineStr"/>
-      <c r="G50" s="1" t="inlineStr"/>
-      <c r="H50" s="1" t="inlineStr"/>
-      <c r="I50" s="1" t="inlineStr"/>
-      <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L444: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A. Hamilton &amp; Co.â€™s Drug Store.</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr"/>
-      <c r="M50" s="1" t="inlineStr"/>
-      <c r="N50" s="1" t="inlineStr"/>
-      <c r="O50" s="1" t="inlineStr"/>
-      <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
-      <c r="R50" s="1" t="inlineStr"/>
-      <c r="S50" s="1" t="inlineStr"/>
-      <c r="T50" s="1" t="inlineStr"/>
-      <c r="U50" s="1" t="inlineStr"/>
-      <c r="V50" s="1" t="inlineStr"/>
-      <c r="W50" s="1" t="inlineStr"/>
-      <c r="X50" s="1" t="inlineStr"/>
-      <c r="Y50" s="1" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr"/>
-      <c r="B51" s="1" t="inlineStr"/>
-      <c r="C51" s="1" t="inlineStr"/>
-      <c r="D51" s="1" t="inlineStr"/>
-      <c r="E51" s="1" t="inlineStr"/>
-      <c r="F51" s="1" t="inlineStr"/>
-      <c r="G51" s="1" t="inlineStr"/>
-      <c r="H51" s="1" t="inlineStr"/>
-      <c r="I51" s="1" t="inlineStr"/>
-      <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: for that same ; althoâ€™, if there was a bit pun</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr"/>
-      <c r="M51" s="1" t="inlineStr"/>
-      <c r="N51" s="1" t="inlineStr"/>
-      <c r="O51" s="1" t="inlineStr"/>
-      <c r="P51" s="1" t="inlineStr"/>
-      <c r="Q51" s="1" t="inlineStr"/>
-      <c r="R51" s="1" t="inlineStr"/>
-      <c r="S51" s="1" t="inlineStr"/>
-      <c r="T51" s="1" t="inlineStr"/>
-      <c r="U51" s="1" t="inlineStr"/>
-      <c r="V51" s="1" t="inlineStr"/>
-      <c r="W51" s="1" t="inlineStr"/>
-      <c r="X51" s="1" t="inlineStr"/>
-      <c r="Y51" s="1" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr"/>
-      <c r="B52" s="1" t="inlineStr"/>
-      <c r="C52" s="1" t="inlineStr"/>
-      <c r="D52" s="1" t="inlineStr"/>
-      <c r="E52" s="1" t="inlineStr"/>
-      <c r="F52" s="1" t="inlineStr"/>
-      <c r="G52" s="1" t="inlineStr"/>
-      <c r="H52" s="1" t="inlineStr"/>
-      <c r="I52" s="1" t="inlineStr"/>
-      <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L454: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™ coffee I widna object. Weel, guid day</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr"/>
-      <c r="M52" s="1" t="inlineStr"/>
-      <c r="N52" s="1" t="inlineStr"/>
-      <c r="O52" s="1" t="inlineStr"/>
-      <c r="P52" s="1" t="inlineStr"/>
-      <c r="Q52" s="1" t="inlineStr"/>
-      <c r="R52" s="1" t="inlineStr"/>
-      <c r="S52" s="1" t="inlineStr"/>
-      <c r="T52" s="1" t="inlineStr"/>
-      <c r="U52" s="1" t="inlineStr"/>
-      <c r="V52" s="1" t="inlineStr"/>
-      <c r="W52" s="1" t="inlineStr"/>
-      <c r="X52" s="1" t="inlineStr"/>
-      <c r="Y52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr"/>
-      <c r="B53" s="1" t="inlineStr"/>
-      <c r="C53" s="1" t="inlineStr"/>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr"/>
-      <c r="G53" s="1" t="inlineStr"/>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr"/>
-      <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L455: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: tae ye ! guid day!" and I camâ€™ oot. Lod,</t>
-        </is>
-      </c>
-      <c r="L53" s="1" t="inlineStr"/>
-      <c r="M53" s="1" t="inlineStr"/>
-      <c r="N53" s="1" t="inlineStr"/>
-      <c r="O53" s="1" t="inlineStr"/>
-      <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
-      <c r="R53" s="1" t="inlineStr"/>
-      <c r="S53" s="1" t="inlineStr"/>
-      <c r="T53" s="1" t="inlineStr"/>
-      <c r="U53" s="1" t="inlineStr"/>
-      <c r="V53" s="1" t="inlineStr"/>
-      <c r="W53" s="1" t="inlineStr"/>
-      <c r="X53" s="1" t="inlineStr"/>
-      <c r="Y53" s="1" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr"/>
-      <c r="B54" s="1" t="inlineStr"/>
-      <c r="C54" s="1" t="inlineStr"/>
-      <c r="D54" s="1" t="inlineStr"/>
-      <c r="E54" s="1" t="inlineStr"/>
-      <c r="F54" s="1" t="inlineStr"/>
-      <c r="G54" s="1" t="inlineStr"/>
-      <c r="H54" s="1" t="inlineStr"/>
-      <c r="I54" s="1" t="inlineStr"/>
-      <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L464: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ye gie ? Yeâ€™re a perfect angel in thae bad</t>
-        </is>
-      </c>
-      <c r="L54" s="1" t="inlineStr"/>
-      <c r="M54" s="1" t="inlineStr"/>
-      <c r="N54" s="1" t="inlineStr"/>
-      <c r="O54" s="1" t="inlineStr"/>
-      <c r="P54" s="1" t="inlineStr"/>
-      <c r="Q54" s="1" t="inlineStr"/>
-      <c r="R54" s="1" t="inlineStr"/>
-      <c r="S54" s="1" t="inlineStr"/>
-      <c r="T54" s="1" t="inlineStr"/>
-      <c r="U54" s="1" t="inlineStr"/>
-      <c r="V54" s="1" t="inlineStr"/>
-      <c r="W54" s="1" t="inlineStr"/>
-      <c r="X54" s="1" t="inlineStr"/>
-      <c r="Y54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr"/>
-      <c r="B55" s="1" t="inlineStr"/>
-      <c r="C55" s="1" t="inlineStr"/>
-      <c r="D55" s="1" t="inlineStr"/>
-      <c r="E55" s="1" t="inlineStr"/>
-      <c r="F55" s="1" t="inlineStr"/>
-      <c r="G55" s="1" t="inlineStr"/>
-      <c r="H55" s="1" t="inlineStr"/>
-      <c r="I55" s="1" t="inlineStr"/>
-      <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L469: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: the tea," he says. "Did ye noâ€™ say it</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr"/>
-      <c r="M55" s="1" t="inlineStr"/>
-      <c r="N55" s="1" t="inlineStr"/>
-      <c r="O55" s="1" t="inlineStr"/>
-      <c r="P55" s="1" t="inlineStr"/>
-      <c r="Q55" s="1" t="inlineStr"/>
-      <c r="R55" s="1" t="inlineStr"/>
-      <c r="S55" s="1" t="inlineStr"/>
-      <c r="T55" s="1" t="inlineStr"/>
-      <c r="U55" s="1" t="inlineStr"/>
-      <c r="V55" s="1" t="inlineStr"/>
-      <c r="W55" s="1" t="inlineStr"/>
-      <c r="X55" s="1" t="inlineStr"/>
-      <c r="Y55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr"/>
-      <c r="B56" s="1" t="inlineStr"/>
-      <c r="C56" s="1" t="inlineStr"/>
-      <c r="D56" s="1" t="inlineStr"/>
-      <c r="E56" s="1" t="inlineStr"/>
-      <c r="F56" s="1" t="inlineStr"/>
-      <c r="G56" s="1" t="inlineStr"/>
-      <c r="H56" s="1" t="inlineStr"/>
-      <c r="I56" s="1" t="inlineStr"/>
-      <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L470: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+FFFD REPLACEMENT CHARACTER :: went alang wiâ€˜ the sugar ?â€� " Certainly.</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr"/>
-      <c r="M56" s="1" t="inlineStr"/>
-      <c r="N56" s="1" t="inlineStr"/>
-      <c r="O56" s="1" t="inlineStr"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
-      <c r="R56" s="1" t="inlineStr"/>
-      <c r="S56" s="1" t="inlineStr"/>
-      <c r="T56" s="1" t="inlineStr"/>
-      <c r="U56" s="1" t="inlineStr"/>
-      <c r="V56" s="1" t="inlineStr"/>
-      <c r="W56" s="1" t="inlineStr"/>
-      <c r="X56" s="1" t="inlineStr"/>
-      <c r="Y56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr"/>
-      <c r="B57" s="1" t="inlineStr"/>
-      <c r="C57" s="1" t="inlineStr"/>
-      <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
-      <c r="F57" s="1" t="inlineStr"/>
-      <c r="G57" s="1" t="inlineStr"/>
-      <c r="H57" s="1" t="inlineStr"/>
-      <c r="I57" s="1" t="inlineStr"/>
-      <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L472: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: naethinâ€™ ?" "Yes." " And whatâ€™s the</t>
-        </is>
-      </c>
-      <c r="L57" s="1" t="inlineStr"/>
-      <c r="M57" s="1" t="inlineStr"/>
-      <c r="N57" s="1" t="inlineStr"/>
-      <c r="O57" s="1" t="inlineStr"/>
-      <c r="P57" s="1" t="inlineStr"/>
-      <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="inlineStr"/>
-      <c r="S57" s="1" t="inlineStr"/>
-      <c r="T57" s="1" t="inlineStr"/>
-      <c r="U57" s="1" t="inlineStr"/>
-      <c r="V57" s="1" t="inlineStr"/>
-      <c r="W57" s="1" t="inlineStr"/>
-      <c r="X57" s="1" t="inlineStr"/>
-      <c r="Y57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr"/>
-      <c r="B58" s="1" t="inlineStr"/>
-      <c r="C58" s="1" t="inlineStr"/>
-      <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
-      <c r="F58" s="1" t="inlineStr"/>
-      <c r="G58" s="1" t="inlineStr"/>
-      <c r="H58" s="1" t="inlineStr"/>
-      <c r="I58" s="1" t="inlineStr"/>
-      <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L473: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: money for, then ?" " For the tea,â€™ he</t>
-        </is>
-      </c>
-      <c r="L58" s="1" t="inlineStr"/>
-      <c r="M58" s="1" t="inlineStr"/>
-      <c r="N58" s="1" t="inlineStr"/>
-      <c r="O58" s="1" t="inlineStr"/>
-      <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="inlineStr"/>
-      <c r="R58" s="1" t="inlineStr"/>
-      <c r="S58" s="1" t="inlineStr"/>
-      <c r="T58" s="1" t="inlineStr"/>
-      <c r="U58" s="1" t="inlineStr"/>
-      <c r="V58" s="1" t="inlineStr"/>
-      <c r="W58" s="1" t="inlineStr"/>
-      <c r="X58" s="1" t="inlineStr"/>
-      <c r="Y58" s="1" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr"/>
-      <c r="B59" s="1" t="inlineStr"/>
-      <c r="C59" s="1" t="inlineStr"/>
-      <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr"/>
-      <c r="F59" s="1" t="inlineStr"/>
-      <c r="G59" s="1" t="inlineStr"/>
-      <c r="H59" s="1" t="inlineStr"/>
-      <c r="I59" s="1" t="inlineStr"/>
-      <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L477: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: crood, " let us understaunâ€™ each either.</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr"/>
-      <c r="M59" s="1" t="inlineStr"/>
-      <c r="N59" s="1" t="inlineStr"/>
-      <c r="O59" s="1" t="inlineStr"/>
-      <c r="P59" s="1" t="inlineStr"/>
-      <c r="Q59" s="1" t="inlineStr"/>
-      <c r="R59" s="1" t="inlineStr"/>
-      <c r="S59" s="1" t="inlineStr"/>
-      <c r="T59" s="1" t="inlineStr"/>
-      <c r="U59" s="1" t="inlineStr"/>
-      <c r="V59" s="1" t="inlineStr"/>
-      <c r="W59" s="1" t="inlineStr"/>
-      <c r="X59" s="1" t="inlineStr"/>
-      <c r="Y59" s="1" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr"/>
-      <c r="B60" s="1" t="inlineStr"/>
-      <c r="C60" s="1" t="inlineStr"/>
-      <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr"/>
-      <c r="F60" s="1" t="inlineStr"/>
-      <c r="G60" s="1" t="inlineStr"/>
-      <c r="H60" s="1" t="inlineStr"/>
-      <c r="I60" s="1" t="inlineStr"/>
-      <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L480: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: no say ye gied sugar for naethinâ€™?â€™ " We</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr"/>
-      <c r="M60" s="1" t="inlineStr"/>
-      <c r="N60" s="1" t="inlineStr"/>
-      <c r="O60" s="1" t="inlineStr"/>
-      <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="inlineStr"/>
-      <c r="S60" s="1" t="inlineStr"/>
-      <c r="T60" s="1" t="inlineStr"/>
-      <c r="U60" s="1" t="inlineStr"/>
-      <c r="V60" s="1" t="inlineStr"/>
-      <c r="W60" s="1" t="inlineStr"/>
-      <c r="X60" s="1" t="inlineStr"/>
-      <c r="Y60" s="1" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr"/>
-      <c r="B61" s="1" t="inlineStr"/>
-      <c r="C61" s="1" t="inlineStr"/>
-      <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr"/>
-      <c r="F61" s="1" t="inlineStr"/>
-      <c r="G61" s="1" t="inlineStr"/>
-      <c r="H61" s="1" t="inlineStr"/>
-      <c r="I61" s="1" t="inlineStr"/>
-      <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L484: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: tea alang wiâ€˜ the sugar."</t>
-        </is>
-      </c>
-      <c r="L61" s="1" t="inlineStr"/>
-      <c r="M61" s="1" t="inlineStr"/>
-      <c r="N61" s="1" t="inlineStr"/>
-      <c r="O61" s="1" t="inlineStr"/>
-      <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="inlineStr"/>
-      <c r="S61" s="1" t="inlineStr"/>
-      <c r="T61" s="1" t="inlineStr"/>
-      <c r="U61" s="1" t="inlineStr"/>
-      <c r="V61" s="1" t="inlineStr"/>
-      <c r="W61" s="1" t="inlineStr"/>
-      <c r="X61" s="1" t="inlineStr"/>
-      <c r="Y61" s="1" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr"/>
-      <c r="B62" s="1" t="inlineStr"/>
-      <c r="C62" s="1" t="inlineStr"/>
-      <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr"/>
-      <c r="F62" s="1" t="inlineStr"/>
-      <c r="G62" s="1" t="inlineStr"/>
-      <c r="H62" s="1" t="inlineStr"/>
-      <c r="I62" s="1" t="inlineStr"/>
-      <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L486: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: : But y're tae pay for the tea.â€™</t>
-        </is>
-      </c>
-      <c r="L62" s="1" t="inlineStr"/>
-      <c r="M62" s="1" t="inlineStr"/>
-      <c r="N62" s="1" t="inlineStr"/>
-      <c r="O62" s="1" t="inlineStr"/>
-      <c r="P62" s="1" t="inlineStr"/>
-      <c r="Q62" s="1" t="inlineStr"/>
-      <c r="R62" s="1" t="inlineStr"/>
-      <c r="S62" s="1" t="inlineStr"/>
-      <c r="T62" s="1" t="inlineStr"/>
-      <c r="U62" s="1" t="inlineStr"/>
-      <c r="V62" s="1" t="inlineStr"/>
-      <c r="W62" s="1" t="inlineStr"/>
-      <c r="X62" s="1" t="inlineStr"/>
-      <c r="Y62" s="1" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr"/>
-      <c r="B63" s="1" t="inlineStr"/>
-      <c r="C63" s="1" t="inlineStr"/>
-      <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr"/>
-      <c r="F63" s="1" t="inlineStr"/>
-      <c r="G63" s="1" t="inlineStr"/>
-      <c r="H63" s="1" t="inlineStr"/>
-      <c r="I63" s="1" t="inlineStr"/>
-      <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L489: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Noo, look here, and pay attention ! Weâ€™ll</t>
-        </is>
-      </c>
-      <c r="L63" s="1" t="inlineStr"/>
-      <c r="M63" s="1" t="inlineStr"/>
-      <c r="N63" s="1" t="inlineStr"/>
-      <c r="O63" s="1" t="inlineStr"/>
-      <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr"/>
-      <c r="R63" s="1" t="inlineStr"/>
-      <c r="S63" s="1" t="inlineStr"/>
-      <c r="T63" s="1" t="inlineStr"/>
-      <c r="U63" s="1" t="inlineStr"/>
-      <c r="V63" s="1" t="inlineStr"/>
-      <c r="W63" s="1" t="inlineStr"/>
-      <c r="X63" s="1" t="inlineStr"/>
-      <c r="Y63" s="1" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr"/>
-      <c r="B64" s="1" t="inlineStr"/>
-      <c r="C64" s="1" t="inlineStr"/>
-      <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr"/>
-      <c r="F64" s="1" t="inlineStr"/>
-      <c r="G64" s="1" t="inlineStr"/>
-      <c r="H64" s="1" t="inlineStr"/>
-      <c r="I64" s="1" t="inlineStr"/>
-      <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L490: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: takâ€™ it backwards this time! Are ye</t>
-        </is>
-      </c>
-      <c r="L64" s="1" t="inlineStr"/>
-      <c r="M64" s="1" t="inlineStr"/>
-      <c r="N64" s="1" t="inlineStr"/>
-      <c r="O64" s="1" t="inlineStr"/>
-      <c r="P64" s="1" t="inlineStr"/>
-      <c r="Q64" s="1" t="inlineStr"/>
-      <c r="R64" s="1" t="inlineStr"/>
-      <c r="S64" s="1" t="inlineStr"/>
-      <c r="T64" s="1" t="inlineStr"/>
-      <c r="U64" s="1" t="inlineStr"/>
-      <c r="V64" s="1" t="inlineStr"/>
-      <c r="W64" s="1" t="inlineStr"/>
-      <c r="X64" s="1" t="inlineStr"/>
-      <c r="Y64" s="1" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr"/>
-      <c r="B65" s="1" t="inlineStr"/>
-      <c r="C65" s="1" t="inlineStr"/>
-      <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr"/>
-      <c r="F65" s="1" t="inlineStr"/>
-      <c r="G65" s="1" t="inlineStr"/>
-      <c r="H65" s="1" t="inlineStr"/>
-      <c r="I65" s="1" t="inlineStr"/>
-      <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L491: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: listening? Didna ye caâ€˜ me back when 1</t>
-        </is>
-      </c>
-      <c r="L65" s="1" t="inlineStr"/>
-      <c r="M65" s="1" t="inlineStr"/>
-      <c r="N65" s="1" t="inlineStr"/>
-      <c r="O65" s="1" t="inlineStr"/>
-      <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr"/>
-      <c r="R65" s="1" t="inlineStr"/>
-      <c r="S65" s="1" t="inlineStr"/>
-      <c r="T65" s="1" t="inlineStr"/>
-      <c r="U65" s="1" t="inlineStr"/>
-      <c r="V65" s="1" t="inlineStr"/>
-      <c r="W65" s="1" t="inlineStr"/>
-      <c r="X65" s="1" t="inlineStr"/>
-      <c r="Y65" s="1" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="inlineStr"/>
-      <c r="B66" s="1" t="inlineStr"/>
-      <c r="C66" s="1" t="inlineStr"/>
-      <c r="D66" s="1" t="inlineStr"/>
-      <c r="E66" s="1" t="inlineStr"/>
-      <c r="F66" s="1" t="inlineStr"/>
-      <c r="G66" s="1" t="inlineStr"/>
-      <c r="H66" s="1" t="inlineStr"/>
-      <c r="I66" s="1" t="inlineStr"/>
-      <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L493: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: sugar, and no askinâ€™ for tea- â€” didna ye cry</t>
-        </is>
-      </c>
-      <c r="L66" s="1" t="inlineStr"/>
-      <c r="M66" s="1" t="inlineStr"/>
-      <c r="N66" s="1" t="inlineStr"/>
-      <c r="O66" s="1" t="inlineStr"/>
-      <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr"/>
-      <c r="R66" s="1" t="inlineStr"/>
-      <c r="S66" s="1" t="inlineStr"/>
-      <c r="T66" s="1" t="inlineStr"/>
-      <c r="U66" s="1" t="inlineStr"/>
-      <c r="V66" s="1" t="inlineStr"/>
-      <c r="W66" s="1" t="inlineStr"/>
-      <c r="X66" s="1" t="inlineStr"/>
-      <c r="Y66" s="1" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr"/>
-      <c r="B67" s="1" t="inlineStr"/>
-      <c r="C67" s="1" t="inlineStr"/>
-      <c r="D67" s="1" t="inlineStr"/>
-      <c r="E67" s="1" t="inlineStr"/>
-      <c r="F67" s="1" t="inlineStr"/>
-      <c r="G67" s="1" t="inlineStr"/>
-      <c r="H67" s="1" t="inlineStr"/>
-      <c r="I67" s="1" t="inlineStr"/>
-      <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L494: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: me back and said ye gied tea alang wiâ€˜ the</t>
-        </is>
-      </c>
-      <c r="L67" s="1" t="inlineStr"/>
-      <c r="M67" s="1" t="inlineStr"/>
-      <c r="N67" s="1" t="inlineStr"/>
-      <c r="O67" s="1" t="inlineStr"/>
-      <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr"/>
-      <c r="R67" s="1" t="inlineStr"/>
-      <c r="S67" s="1" t="inlineStr"/>
-      <c r="T67" s="1" t="inlineStr"/>
-      <c r="U67" s="1" t="inlineStr"/>
-      <c r="V67" s="1" t="inlineStr"/>
-      <c r="W67" s="1" t="inlineStr"/>
-      <c r="X67" s="1" t="inlineStr"/>
-      <c r="Y67" s="1" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr"/>
-      <c r="B68" s="1" t="inlineStr"/>
-      <c r="C68" s="1" t="inlineStr"/>
-      <c r="D68" s="1" t="inlineStr"/>
-      <c r="E68" s="1" t="inlineStr"/>
-      <c r="F68" s="1" t="inlineStr"/>
-      <c r="G68" s="1" t="inlineStr"/>
-      <c r="H68" s="1" t="inlineStr"/>
-      <c r="I68" s="1" t="inlineStr"/>
-      <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L497: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Â« I did.â€�</t>
-        </is>
-      </c>
-      <c r="L68" s="1" t="inlineStr"/>
-      <c r="M68" s="1" t="inlineStr"/>
-      <c r="N68" s="1" t="inlineStr"/>
-      <c r="O68" s="1" t="inlineStr"/>
-      <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="inlineStr"/>
-      <c r="R68" s="1" t="inlineStr"/>
-      <c r="S68" s="1" t="inlineStr"/>
-      <c r="T68" s="1" t="inlineStr"/>
-      <c r="U68" s="1" t="inlineStr"/>
-      <c r="V68" s="1" t="inlineStr"/>
-      <c r="W68" s="1" t="inlineStr"/>
-      <c r="X68" s="1" t="inlineStr"/>
-      <c r="Y68" s="1" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="inlineStr"/>
-      <c r="B69" s="1" t="inlineStr"/>
-      <c r="C69" s="1" t="inlineStr"/>
-      <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
-      <c r="F69" s="1" t="inlineStr"/>
-      <c r="G69" s="1" t="inlineStr"/>
-      <c r="H69" s="1" t="inlineStr"/>
-      <c r="I69" s="1" t="inlineStr"/>
-      <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L504: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: yourselâ€™, eh? It's no the worth ot, min</t>
-        </is>
-      </c>
-      <c r="L69" s="1" t="inlineStr"/>
-      <c r="M69" s="1" t="inlineStr"/>
-      <c r="N69" s="1" t="inlineStr"/>
-      <c r="O69" s="1" t="inlineStr"/>
-      <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="inlineStr"/>
-      <c r="R69" s="1" t="inlineStr"/>
-      <c r="S69" s="1" t="inlineStr"/>
-      <c r="T69" s="1" t="inlineStr"/>
-      <c r="U69" s="1" t="inlineStr"/>
-      <c r="V69" s="1" t="inlineStr"/>
-      <c r="W69" s="1" t="inlineStr"/>
-      <c r="X69" s="1" t="inlineStr"/>
-      <c r="Y69" s="1" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="inlineStr"/>
-      <c r="B70" s="1" t="inlineStr"/>
-      <c r="C70" s="1" t="inlineStr"/>
-      <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
-      <c r="F70" s="1" t="inlineStr"/>
-      <c r="G70" s="1" t="inlineStr"/>
-      <c r="H70" s="1" t="inlineStr"/>
-      <c r="I70" s="1" t="inlineStr"/>
-      <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™ ; hooever, there's my cardâ€”ye can sum-</t>
-        </is>
-      </c>
-      <c r="L70" s="1" t="inlineStr"/>
-      <c r="M70" s="1" t="inlineStr"/>
-      <c r="N70" s="1" t="inlineStr"/>
-      <c r="O70" s="1" t="inlineStr"/>
-      <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr"/>
-      <c r="R70" s="1" t="inlineStr"/>
-      <c r="S70" s="1" t="inlineStr"/>
-      <c r="T70" s="1" t="inlineStr"/>
-      <c r="U70" s="1" t="inlineStr"/>
-      <c r="V70" s="1" t="inlineStr"/>
-      <c r="W70" s="1" t="inlineStr"/>
-      <c r="X70" s="1" t="inlineStr"/>
-      <c r="Y70" s="1" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="inlineStr"/>
-      <c r="B71" s="1" t="inlineStr"/>
-      <c r="C71" s="1" t="inlineStr"/>
-      <c r="D71" s="1" t="inlineStr"/>
-      <c r="E71" s="1" t="inlineStr"/>
-      <c r="F71" s="1" t="inlineStr"/>
-      <c r="G71" s="1" t="inlineStr"/>
-      <c r="H71" s="1" t="inlineStr"/>
-      <c r="I71" s="1" t="inlineStr"/>
-      <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L507: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: mon me, but I'm thinking yeâ€™ll get the</t>
-        </is>
-      </c>
-      <c r="L71" s="1" t="inlineStr"/>
-      <c r="M71" s="1" t="inlineStr"/>
-      <c r="N71" s="1" t="inlineStr"/>
-      <c r="O71" s="1" t="inlineStr"/>
-      <c r="P71" s="1" t="inlineStr"/>
-      <c r="Q71" s="1" t="inlineStr"/>
-      <c r="R71" s="1" t="inlineStr"/>
-      <c r="S71" s="1" t="inlineStr"/>
-      <c r="T71" s="1" t="inlineStr"/>
-      <c r="U71" s="1" t="inlineStr"/>
-      <c r="V71" s="1" t="inlineStr"/>
-      <c r="W71" s="1" t="inlineStr"/>
-      <c r="X71" s="1" t="inlineStr"/>
-      <c r="Y71" s="1" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr"/>
-      <c r="B72" s="1" t="inlineStr"/>
-      <c r="C72" s="1" t="inlineStr"/>
-      <c r="D72" s="1" t="inlineStr"/>
-      <c r="E72" s="1" t="inlineStr"/>
-      <c r="F72" s="1" t="inlineStr"/>
-      <c r="G72" s="1" t="inlineStr"/>
-      <c r="H72" s="1" t="inlineStr"/>
-      <c r="I72" s="1" t="inlineStr"/>
-      <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L508: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: warst oâ€™t. Na, na! I wisna burn yester-</t>
-        </is>
-      </c>
-      <c r="L72" s="1" t="inlineStr"/>
-      <c r="M72" s="1" t="inlineStr"/>
-      <c r="N72" s="1" t="inlineStr"/>
-      <c r="O72" s="1" t="inlineStr"/>
-      <c r="P72" s="1" t="inlineStr"/>
-      <c r="Q72" s="1" t="inlineStr"/>
-      <c r="R72" s="1" t="inlineStr"/>
-      <c r="S72" s="1" t="inlineStr"/>
-      <c r="T72" s="1" t="inlineStr"/>
-      <c r="U72" s="1" t="inlineStr"/>
-      <c r="V72" s="1" t="inlineStr"/>
-      <c r="W72" s="1" t="inlineStr"/>
-      <c r="X72" s="1" t="inlineStr"/>
-      <c r="Y72" s="1" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="inlineStr"/>
-      <c r="B73" s="1" t="inlineStr"/>
-      <c r="C73" s="1" t="inlineStr"/>
-      <c r="D73" s="1" t="inlineStr"/>
-      <c r="E73" s="1" t="inlineStr"/>
-      <c r="F73" s="1" t="inlineStr"/>
-      <c r="G73" s="1" t="inlineStr"/>
-      <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
-      <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L510: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: nee about it Come awaâ€™, Betty, hereâ€™s</t>
-        </is>
-      </c>
-      <c r="L73" s="1" t="inlineStr"/>
-      <c r="M73" s="1" t="inlineStr"/>
-      <c r="N73" s="1" t="inlineStr"/>
-      <c r="O73" s="1" t="inlineStr"/>
-      <c r="P73" s="1" t="inlineStr"/>
-      <c r="Q73" s="1" t="inlineStr"/>
-      <c r="R73" s="1" t="inlineStr"/>
-      <c r="S73" s="1" t="inlineStr"/>
-      <c r="T73" s="1" t="inlineStr"/>
-      <c r="U73" s="1" t="inlineStr"/>
-      <c r="V73" s="1" t="inlineStr"/>
-      <c r="W73" s="1" t="inlineStr"/>
-      <c r="X73" s="1" t="inlineStr"/>
-      <c r="Y73" s="1" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="inlineStr"/>
-      <c r="B74" s="1" t="inlineStr"/>
-      <c r="C74" s="1" t="inlineStr"/>
-      <c r="D74" s="1" t="inlineStr"/>
-      <c r="E74" s="1" t="inlineStr"/>
-      <c r="F74" s="1" t="inlineStr"/>
-      <c r="G74" s="1" t="inlineStr"/>
-      <c r="H74" s="1" t="inlineStr"/>
-      <c r="I74" s="1" t="inlineStr"/>
-      <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L511: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: oor caur;â€� and the crood " hoorahed,â€�</t>
-        </is>
-      </c>
-      <c r="L74" s="1" t="inlineStr"/>
-      <c r="M74" s="1" t="inlineStr"/>
-      <c r="N74" s="1" t="inlineStr"/>
-      <c r="O74" s="1" t="inlineStr"/>
-      <c r="P74" s="1" t="inlineStr"/>
-      <c r="Q74" s="1" t="inlineStr"/>
-      <c r="R74" s="1" t="inlineStr"/>
-      <c r="S74" s="1" t="inlineStr"/>
-      <c r="T74" s="1" t="inlineStr"/>
-      <c r="U74" s="1" t="inlineStr"/>
-      <c r="V74" s="1" t="inlineStr"/>
-      <c r="W74" s="1" t="inlineStr"/>
-      <c r="X74" s="1" t="inlineStr"/>
-      <c r="Y74" s="1" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr"/>
-      <c r="B75" s="1" t="inlineStr"/>
-      <c r="C75" s="1" t="inlineStr"/>
-      <c r="D75" s="1" t="inlineStr"/>
-      <c r="E75" s="1" t="inlineStr"/>
-      <c r="F75" s="1" t="inlineStr"/>
-      <c r="G75" s="1" t="inlineStr"/>
-      <c r="H75" s="1" t="inlineStr"/>
-      <c r="I75" s="1" t="inlineStr"/>
-      <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L512: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and the policeman threatened tae takâ€™ him</t>
-        </is>
-      </c>
-      <c r="L75" s="1" t="inlineStr"/>
-      <c r="M75" s="1" t="inlineStr"/>
-      <c r="N75" s="1" t="inlineStr"/>
-      <c r="O75" s="1" t="inlineStr"/>
-      <c r="P75" s="1" t="inlineStr"/>
-      <c r="Q75" s="1" t="inlineStr"/>
-      <c r="R75" s="1" t="inlineStr"/>
-      <c r="S75" s="1" t="inlineStr"/>
-      <c r="T75" s="1" t="inlineStr"/>
-      <c r="U75" s="1" t="inlineStr"/>
-      <c r="V75" s="1" t="inlineStr"/>
-      <c r="W75" s="1" t="inlineStr"/>
-      <c r="X75" s="1" t="inlineStr"/>
-      <c r="Y75" s="1" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr"/>
-      <c r="B76" s="1" t="inlineStr"/>
-      <c r="C76" s="1" t="inlineStr"/>
-      <c r="D76" s="1" t="inlineStr"/>
-      <c r="E76" s="1" t="inlineStr"/>
-      <c r="F76" s="1" t="inlineStr"/>
-      <c r="G76" s="1" t="inlineStr"/>
-      <c r="H76" s="1" t="inlineStr"/>
-      <c r="I76" s="1" t="inlineStr"/>
-      <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L514: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: camâ€™ awaâ€™.â€” Glasgow Bailie.</t>
-        </is>
-      </c>
-      <c r="L76" s="1" t="inlineStr"/>
-      <c r="M76" s="1" t="inlineStr"/>
-      <c r="N76" s="1" t="inlineStr"/>
-      <c r="O76" s="1" t="inlineStr"/>
-      <c r="P76" s="1" t="inlineStr"/>
-      <c r="Q76" s="1" t="inlineStr"/>
-      <c r="R76" s="1" t="inlineStr"/>
-      <c r="S76" s="1" t="inlineStr"/>
-      <c r="T76" s="1" t="inlineStr"/>
-      <c r="U76" s="1" t="inlineStr"/>
-      <c r="V76" s="1" t="inlineStr"/>
-      <c r="W76" s="1" t="inlineStr"/>
-      <c r="X76" s="1" t="inlineStr"/>
-      <c r="Y76" s="1" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr"/>
-      <c r="B77" s="1" t="inlineStr"/>
-      <c r="C77" s="1" t="inlineStr"/>
-      <c r="D77" s="1" t="inlineStr"/>
-      <c r="E77" s="1" t="inlineStr"/>
-      <c r="F77" s="1" t="inlineStr"/>
-      <c r="G77" s="1" t="inlineStr"/>
-      <c r="H77" s="1" t="inlineStr"/>
-      <c r="I77" s="1" t="inlineStr"/>
-      <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L564: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ located at</t>
-        </is>
-      </c>
-      <c r="L77" s="1" t="inlineStr"/>
-      <c r="M77" s="1" t="inlineStr"/>
-      <c r="N77" s="1" t="inlineStr"/>
-      <c r="O77" s="1" t="inlineStr"/>
-      <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
-      <c r="S77" s="1" t="inlineStr"/>
-      <c r="T77" s="1" t="inlineStr"/>
-      <c r="U77" s="1" t="inlineStr"/>
-      <c r="V77" s="1" t="inlineStr"/>
-      <c r="W77" s="1" t="inlineStr"/>
-      <c r="X77" s="1" t="inlineStr"/>
-      <c r="Y77" s="1" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr"/>
-      <c r="B78" s="1" t="inlineStr"/>
-      <c r="C78" s="1" t="inlineStr"/>
-      <c r="D78" s="1" t="inlineStr"/>
-      <c r="E78" s="1" t="inlineStr"/>
-      <c r="F78" s="1" t="inlineStr"/>
-      <c r="G78" s="1" t="inlineStr"/>
-      <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
-      <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+FFFD REPLACEMENT CHARACTER :: â€˜* TIMESâ€� NEW BUILDING.</t>
-        </is>
-      </c>
-      <c r="L78" s="1" t="inlineStr"/>
-      <c r="M78" s="1" t="inlineStr"/>
-      <c r="N78" s="1" t="inlineStr"/>
-      <c r="O78" s="1" t="inlineStr"/>
-      <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="inlineStr"/>
-      <c r="R78" s="1" t="inlineStr"/>
-      <c r="S78" s="1" t="inlineStr"/>
-      <c r="T78" s="1" t="inlineStr"/>
-      <c r="U78" s="1" t="inlineStr"/>
-      <c r="V78" s="1" t="inlineStr"/>
-      <c r="W78" s="1" t="inlineStr"/>
-      <c r="X78" s="1" t="inlineStr"/>
-      <c r="Y78" s="1" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="inlineStr"/>
-      <c r="B79" s="1" t="inlineStr"/>
-      <c r="C79" s="1" t="inlineStr"/>
-      <c r="D79" s="1" t="inlineStr"/>
-      <c r="E79" s="1" t="inlineStr"/>
-      <c r="F79" s="1" t="inlineStr"/>
-      <c r="G79" s="1" t="inlineStr"/>
-      <c r="H79" s="1" t="inlineStr"/>
-      <c r="I79" s="1" t="inlineStr"/>
-      <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: street known as the â€œClay Wharf." A large and</t>
-        </is>
-      </c>
-      <c r="L79" s="1" t="inlineStr"/>
-      <c r="M79" s="1" t="inlineStr"/>
-      <c r="N79" s="1" t="inlineStr"/>
-      <c r="O79" s="1" t="inlineStr"/>
-      <c r="P79" s="1" t="inlineStr"/>
-      <c r="Q79" s="1" t="inlineStr"/>
-      <c r="R79" s="1" t="inlineStr"/>
-      <c r="S79" s="1" t="inlineStr"/>
-      <c r="T79" s="1" t="inlineStr"/>
-      <c r="U79" s="1" t="inlineStr"/>
-      <c r="V79" s="1" t="inlineStr"/>
-      <c r="W79" s="1" t="inlineStr"/>
-      <c r="X79" s="1" t="inlineStr"/>
-      <c r="Y79" s="1" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="inlineStr"/>
-      <c r="B80" s="1" t="inlineStr"/>
-      <c r="C80" s="1" t="inlineStr"/>
-      <c r="D80" s="1" t="inlineStr"/>
-      <c r="E80" s="1" t="inlineStr"/>
-      <c r="F80" s="1" t="inlineStr"/>
-      <c r="G80" s="1" t="inlineStr"/>
-      <c r="H80" s="1" t="inlineStr"/>
-      <c r="I80" s="1" t="inlineStr"/>
-      <c r="J80" s="1" t="inlineStr"/>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>L628: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: NIAGARA FALLS, Ont., July 7.â€”Avery</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr"/>
-      <c r="M80" s="1" t="inlineStr"/>
-      <c r="N80" s="1" t="inlineStr"/>
-      <c r="O80" s="1" t="inlineStr"/>
-      <c r="P80" s="1" t="inlineStr"/>
-      <c r="Q80" s="1" t="inlineStr"/>
-      <c r="R80" s="1" t="inlineStr"/>
-      <c r="S80" s="1" t="inlineStr"/>
-      <c r="T80" s="1" t="inlineStr"/>
-      <c r="U80" s="1" t="inlineStr"/>
-      <c r="V80" s="1" t="inlineStr"/>
-      <c r="W80" s="1" t="inlineStr"/>
-      <c r="X80" s="1" t="inlineStr"/>
-      <c r="Y80" s="1" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="inlineStr"/>
-      <c r="B81" s="1" t="inlineStr"/>
-      <c r="C81" s="1" t="inlineStr"/>
-      <c r="D81" s="1" t="inlineStr"/>
-      <c r="E81" s="1" t="inlineStr"/>
-      <c r="F81" s="1" t="inlineStr"/>
-      <c r="G81" s="1" t="inlineStr"/>
-      <c r="H81" s="1" t="inlineStr"/>
-      <c r="I81" s="1" t="inlineStr"/>
-      <c r="J81" s="1" t="inlineStr"/>
-      <c r="K81" s="1" t="inlineStr">
-        <is>
-          <t>L697: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TONEY TO LOAN.â€”ABOUT</t>
-        </is>
-      </c>
-      <c r="L81" s="1" t="inlineStr"/>
-      <c r="M81" s="1" t="inlineStr"/>
-      <c r="N81" s="1" t="inlineStr"/>
-      <c r="O81" s="1" t="inlineStr"/>
-      <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
-      <c r="R81" s="1" t="inlineStr"/>
-      <c r="S81" s="1" t="inlineStr"/>
-      <c r="T81" s="1" t="inlineStr"/>
-      <c r="U81" s="1" t="inlineStr"/>
-      <c r="V81" s="1" t="inlineStr"/>
-      <c r="W81" s="1" t="inlineStr"/>
-      <c r="X81" s="1" t="inlineStr"/>
-      <c r="Y81" s="1" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="inlineStr"/>
-      <c r="B82" s="1" t="inlineStr"/>
-      <c r="C82" s="1" t="inlineStr"/>
-      <c r="D82" s="1" t="inlineStr"/>
-      <c r="E82" s="1" t="inlineStr"/>
-      <c r="F82" s="1" t="inlineStr"/>
-      <c r="G82" s="1" t="inlineStr"/>
-      <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr"/>
-      <c r="J82" s="1" t="inlineStr"/>
-      <c r="K82" s="1" t="inlineStr">
-        <is>
-          <t>L717: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Secretary of the Alliance. Mr. Mathewsâ€™</t>
-        </is>
-      </c>
-      <c r="L82" s="1" t="inlineStr"/>
-      <c r="M82" s="1" t="inlineStr"/>
-      <c r="N82" s="1" t="inlineStr"/>
-      <c r="O82" s="1" t="inlineStr"/>
-      <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
-      <c r="R82" s="1" t="inlineStr"/>
-      <c r="S82" s="1" t="inlineStr"/>
-      <c r="T82" s="1" t="inlineStr"/>
-      <c r="U82" s="1" t="inlineStr"/>
-      <c r="V82" s="1" t="inlineStr"/>
-      <c r="W82" s="1" t="inlineStr"/>
-      <c r="X82" s="1" t="inlineStr"/>
-      <c r="Y82" s="1" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="inlineStr"/>
-      <c r="B83" s="1" t="inlineStr"/>
-      <c r="C83" s="1" t="inlineStr"/>
-      <c r="D83" s="1" t="inlineStr"/>
-      <c r="E83" s="1" t="inlineStr"/>
-      <c r="F83" s="1" t="inlineStr"/>
-      <c r="G83" s="1" t="inlineStr"/>
-      <c r="H83" s="1" t="inlineStr"/>
-      <c r="I83" s="1" t="inlineStr"/>
-      <c r="J83" s="1" t="inlineStr"/>
-      <c r="K83" s="1" t="inlineStr">
-        <is>
-          <t>L729: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Mr. C. Lowell, proprietor of Queenâ€™s</t>
-        </is>
-      </c>
-      <c r="L83" s="1" t="inlineStr"/>
-      <c r="M83" s="1" t="inlineStr"/>
-      <c r="N83" s="1" t="inlineStr"/>
-      <c r="O83" s="1" t="inlineStr"/>
-      <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
-      <c r="R83" s="1" t="inlineStr"/>
-      <c r="S83" s="1" t="inlineStr"/>
-      <c r="T83" s="1" t="inlineStr"/>
-      <c r="U83" s="1" t="inlineStr"/>
-      <c r="V83" s="1" t="inlineStr"/>
-      <c r="W83" s="1" t="inlineStr"/>
-      <c r="X83" s="1" t="inlineStr"/>
-      <c r="Y83" s="1" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr"/>
-      <c r="B84" s="1" t="inlineStr"/>
-      <c r="C84" s="1" t="inlineStr"/>
-      <c r="D84" s="1" t="inlineStr"/>
-      <c r="E84" s="1" t="inlineStr"/>
-      <c r="F84" s="1" t="inlineStr"/>
-      <c r="G84" s="1" t="inlineStr"/>
-      <c r="H84" s="1" t="inlineStr"/>
-      <c r="I84" s="1" t="inlineStr"/>
-      <c r="J84" s="1" t="inlineStr"/>
-      <c r="K84" s="1" t="inlineStr">
-        <is>
-          <t>L746: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: A. Murray &amp; Co.â€™s, opposite fountain.____</t>
-        </is>
-      </c>
-      <c r="L84" s="1" t="inlineStr"/>
-      <c r="M84" s="1" t="inlineStr"/>
-      <c r="N84" s="1" t="inlineStr"/>
-      <c r="O84" s="1" t="inlineStr"/>
-      <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr"/>
-      <c r="R84" s="1" t="inlineStr"/>
-      <c r="S84" s="1" t="inlineStr"/>
-      <c r="T84" s="1" t="inlineStr"/>
-      <c r="U84" s="1" t="inlineStr"/>
-      <c r="V84" s="1" t="inlineStr"/>
-      <c r="W84" s="1" t="inlineStr"/>
-      <c r="X84" s="1" t="inlineStr"/>
-      <c r="Y84" s="1" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr"/>
-      <c r="B85" s="1" t="inlineStr"/>
-      <c r="C85" s="1" t="inlineStr"/>
-      <c r="D85" s="1" t="inlineStr"/>
-      <c r="E85" s="1" t="inlineStr"/>
-      <c r="F85" s="1" t="inlineStr"/>
-      <c r="G85" s="1" t="inlineStr"/>
-      <c r="H85" s="1" t="inlineStr"/>
-      <c r="I85" s="1" t="inlineStr"/>
-      <c r="J85" s="1" t="inlineStr"/>
-      <c r="K85" s="1" t="inlineStr">
-        <is>
-          <t>L751: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: oâ€™clock on August 1st, at Abingdon village.</t>
-        </is>
-      </c>
-      <c r="L85" s="1" t="inlineStr"/>
-      <c r="M85" s="1" t="inlineStr"/>
-      <c r="N85" s="1" t="inlineStr"/>
-      <c r="O85" s="1" t="inlineStr"/>
-      <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
-      <c r="R85" s="1" t="inlineStr"/>
-      <c r="S85" s="1" t="inlineStr"/>
-      <c r="T85" s="1" t="inlineStr"/>
-      <c r="U85" s="1" t="inlineStr"/>
-      <c r="V85" s="1" t="inlineStr"/>
-      <c r="W85" s="1" t="inlineStr"/>
-      <c r="X85" s="1" t="inlineStr"/>
-      <c r="Y85" s="1" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="inlineStr"/>
-      <c r="B86" s="1" t="inlineStr"/>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr"/>
-      <c r="G86" s="1" t="inlineStr"/>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr"/>
-      <c r="J86" s="1" t="inlineStr"/>
-      <c r="K86" s="1" t="inlineStr">
-        <is>
-          <t>L756: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Notaries, etc. Officeâ€”Canada Life Chambers,</t>
-        </is>
-      </c>
-      <c r="L86" s="1" t="inlineStr"/>
-      <c r="M86" s="1" t="inlineStr"/>
-      <c r="N86" s="1" t="inlineStr"/>
-      <c r="O86" s="1" t="inlineStr"/>
-      <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
-      <c r="R86" s="1" t="inlineStr"/>
-      <c r="S86" s="1" t="inlineStr"/>
-      <c r="T86" s="1" t="inlineStr"/>
-      <c r="U86" s="1" t="inlineStr"/>
-      <c r="V86" s="1" t="inlineStr"/>
-      <c r="W86" s="1" t="inlineStr"/>
-      <c r="X86" s="1" t="inlineStr"/>
-      <c r="Y86" s="1" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="inlineStr"/>
-      <c r="B87" s="1" t="inlineStr"/>
-      <c r="C87" s="1" t="inlineStr"/>
-      <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
-      <c r="F87" s="1" t="inlineStr"/>
-      <c r="G87" s="1" t="inlineStr"/>
-      <c r="H87" s="1" t="inlineStr"/>
-      <c r="I87" s="1" t="inlineStr"/>
-      <c r="J87" s="1" t="inlineStr"/>
-      <c r="K87" s="1" t="inlineStr">
-        <is>
-          <t>L769: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: and good fortune. â€”Brantford Expositor.</t>
-        </is>
-      </c>
-      <c r="L87" s="1" t="inlineStr"/>
-      <c r="M87" s="1" t="inlineStr"/>
-      <c r="N87" s="1" t="inlineStr"/>
-      <c r="O87" s="1" t="inlineStr"/>
-      <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="inlineStr"/>
-      <c r="S87" s="1" t="inlineStr"/>
-      <c r="T87" s="1" t="inlineStr"/>
-      <c r="U87" s="1" t="inlineStr"/>
-      <c r="V87" s="1" t="inlineStr"/>
-      <c r="W87" s="1" t="inlineStr"/>
-      <c r="X87" s="1" t="inlineStr"/>
-      <c r="Y87" s="1" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="inlineStr"/>
-      <c r="B88" s="1" t="inlineStr"/>
-      <c r="C88" s="1" t="inlineStr"/>
-      <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
-      <c r="F88" s="1" t="inlineStr"/>
-      <c r="G88" s="1" t="inlineStr"/>
-      <c r="H88" s="1" t="inlineStr"/>
-      <c r="I88" s="1" t="inlineStr"/>
-      <c r="J88" s="1" t="inlineStr"/>
-      <c r="K88" s="1" t="inlineStr">
-        <is>
-          <t>L786: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 00â€™8, Jewellers, 42 King street west._____________</t>
-        </is>
-      </c>
-      <c r="L88" s="1" t="inlineStr"/>
-      <c r="M88" s="1" t="inlineStr"/>
-      <c r="N88" s="1" t="inlineStr"/>
-      <c r="O88" s="1" t="inlineStr"/>
-      <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
-      <c r="R88" s="1" t="inlineStr"/>
-      <c r="S88" s="1" t="inlineStr"/>
-      <c r="T88" s="1" t="inlineStr"/>
-      <c r="U88" s="1" t="inlineStr"/>
-      <c r="V88" s="1" t="inlineStr"/>
-      <c r="W88" s="1" t="inlineStr"/>
-      <c r="X88" s="1" t="inlineStr"/>
-      <c r="Y88" s="1" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="inlineStr"/>
-      <c r="B89" s="1" t="inlineStr"/>
-      <c r="C89" s="1" t="inlineStr"/>
-      <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
-      <c r="F89" s="1" t="inlineStr"/>
-      <c r="G89" s="1" t="inlineStr"/>
-      <c r="H89" s="1" t="inlineStr"/>
-      <c r="I89" s="1" t="inlineStr"/>
-      <c r="J89" s="1" t="inlineStr"/>
-      <c r="K89" s="1" t="inlineStr">
-        <is>
-          <t>L790: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No commission or agentâ€™s fees charged, Apply</t>
-        </is>
-      </c>
-      <c r="L89" s="1" t="inlineStr"/>
-      <c r="M89" s="1" t="inlineStr"/>
-      <c r="N89" s="1" t="inlineStr"/>
-      <c r="O89" s="1" t="inlineStr"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
-      <c r="S89" s="1" t="inlineStr"/>
-      <c r="T89" s="1" t="inlineStr"/>
-      <c r="U89" s="1" t="inlineStr"/>
-      <c r="V89" s="1" t="inlineStr"/>
-      <c r="W89" s="1" t="inlineStr"/>
-      <c r="X89" s="1" t="inlineStr"/>
-      <c r="Y89" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
